--- a/data/gold/results/01_eriksen_replication/full_results_tables.xlsx
+++ b/data/gold/results/01_eriksen_replication/full_results_tables.xlsx
@@ -462,19 +462,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>202.3267917257008</v>
+        <v>427.7509388962222</v>
       </c>
       <c r="C2">
-        <v>206.6101087752129</v>
+        <v>140.043890559487</v>
       </c>
       <c r="D2">
-        <v>6.51880060624706</v>
+        <v>20.07859838686123</v>
       </c>
       <c r="E2">
-        <v>581.7107327374586</v>
+        <v>1581.30551358638</v>
       </c>
       <c r="F2">
-        <v>90.06703665493437</v>
+        <v>168.4117598594563</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -482,19 +482,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>204.9413729810275</v>
+        <v>73.2482410825739</v>
       </c>
       <c r="C3">
-        <v>14.37467498741655</v>
+        <v>30.35294647038642</v>
       </c>
       <c r="D3">
-        <v>0.1946795840814501</v>
+        <v>0.2897276114387822</v>
       </c>
       <c r="E3">
-        <v>6.743675143091359</v>
+        <v>14.75781639340486</v>
       </c>
       <c r="F3">
-        <v>9.366207192124389</v>
+        <v>2.366540851442613</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -522,19 +522,19 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>933.9296628156776</v>
+        <v>197.8793966534408</v>
       </c>
       <c r="C5">
-        <v>811.9936650102653</v>
+        <v>176.4913934655891</v>
       </c>
       <c r="D5">
-        <v>6.662731658726979</v>
+        <v>2.609842445146032</v>
       </c>
       <c r="E5">
-        <v>538.9594219695125</v>
+        <v>130.9241583599658</v>
       </c>
       <c r="F5">
-        <v>236.5860920398866</v>
+        <v>50.96721475057531</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -562,19 +562,19 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>1627.759475004623</v>
+        <v>1686.434481586272</v>
       </c>
       <c r="C7">
-        <v>3465.252911727226</v>
+        <v>2192.44277573989</v>
       </c>
       <c r="D7">
-        <v>23.82886154964101</v>
+        <v>56.75597006504326</v>
       </c>
       <c r="E7">
-        <v>1949.992931595298</v>
+        <v>2045.663178932456</v>
       </c>
       <c r="F7">
-        <v>823.297718807123</v>
+        <v>354.2507215739509</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -582,19 +582,19 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>300.9951287114616</v>
+        <v>611.0199164181031</v>
       </c>
       <c r="C8">
-        <v>301.9165135385996</v>
+        <v>365.374681464406</v>
       </c>
       <c r="D8">
-        <v>3.08323202186992</v>
+        <v>10.70547195169472</v>
       </c>
       <c r="E8">
-        <v>314.6529525585728</v>
+        <v>692.5948768233908</v>
       </c>
       <c r="F8">
-        <v>69.52820048025472</v>
+        <v>103.0264837648855</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -602,19 +602,19 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>342.995812733584</v>
+        <v>587.7811144201161</v>
       </c>
       <c r="C9">
-        <v>167.0885354213826</v>
+        <v>130.9182134157388</v>
       </c>
       <c r="D9">
-        <v>0.7740550608896813</v>
+        <v>2.521025603167286</v>
       </c>
       <c r="E9">
-        <v>86.19759323966218</v>
+        <v>180.9225710033792</v>
       </c>
       <c r="F9">
-        <v>18.52895129563261</v>
+        <v>33.38925533550565</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -622,19 +622,19 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>513.6708915572244</v>
+        <v>286.654338371472</v>
       </c>
       <c r="C10">
-        <v>600.4577098396339</v>
+        <v>1198.125221424649</v>
       </c>
       <c r="D10">
-        <v>1.766174844054563</v>
+        <v>2.366717012212403</v>
       </c>
       <c r="E10">
-        <v>353.1607737129829</v>
+        <v>207.6228127182082</v>
       </c>
       <c r="F10">
-        <v>189.3270404239644</v>
+        <v>77.74000040063899</v>
       </c>
     </row>
   </sheetData>
@@ -672,19 +672,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>4.159583920515873</v>
+        <v>9.282264530973327</v>
       </c>
       <c r="C2">
-        <v>3.692614168981701</v>
+        <v>3.286427011471938</v>
       </c>
       <c r="D2">
-        <v>15.1530819750613</v>
+        <v>21.02064861852112</v>
       </c>
       <c r="E2">
-        <v>15.17554894591368</v>
+        <v>32.56674650246919</v>
       </c>
       <c r="F2">
-        <v>6.087838845614857</v>
+        <v>20.21970651268073</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -692,19 +692,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>4.213336416939002</v>
+        <v>1.589498673951277</v>
       </c>
       <c r="C3">
-        <v>0.256909639357439</v>
+        <v>0.712296286253683</v>
       </c>
       <c r="D3">
-        <v>0.4525365745394989</v>
+        <v>0.3033210883446589</v>
       </c>
       <c r="E3">
-        <v>0.1759275984607157</v>
+        <v>0.3039349836477669</v>
       </c>
       <c r="F3">
-        <v>0.633083557514471</v>
+        <v>0.2841295732932891</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -712,16 +712,16 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>12.4634894632463</v>
+        <v>13.15546261394286</v>
       </c>
       <c r="C4">
-        <v>0.4920605513527713</v>
+        <v>0.6460944456460246</v>
       </c>
       <c r="D4">
-        <v>0.4442157599757189</v>
+        <v>0.2000660540940949</v>
       </c>
       <c r="E4">
-        <v>0.04675975944719598</v>
+        <v>0.03691420533824447</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -732,19 +732,19 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>19.20041718255268</v>
+        <v>4.294014899666319</v>
       </c>
       <c r="C5">
-        <v>14.51225852556157</v>
+        <v>4.141744994803999</v>
       </c>
       <c r="D5">
-        <v>15.48765257611558</v>
+        <v>2.732291364770544</v>
       </c>
       <c r="E5">
-        <v>14.06026161743707</v>
+        <v>2.696363125104114</v>
       </c>
       <c r="F5">
-        <v>15.99139990550279</v>
+        <v>6.119181492346005</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -752,7 +752,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>2.698420356824386</v>
+        <v>2.848236701734999</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>2.89004739998922</v>
+        <v>5.133459330188053</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -772,19 +772,19 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>33.46468394495142</v>
+        <v>36.59590090586916</v>
       </c>
       <c r="C7">
-        <v>61.93231336454421</v>
+        <v>51.45032125651682</v>
       </c>
       <c r="D7">
-        <v>55.390663750026</v>
+        <v>59.41885388380837</v>
       </c>
       <c r="E7">
-        <v>50.87101116108492</v>
+        <v>42.13012198169974</v>
       </c>
       <c r="F7">
-        <v>55.6485926506333</v>
+        <v>42.53174260579089</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -792,19 +792,19 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>6.188080613857538</v>
+        <v>13.2592309733353</v>
       </c>
       <c r="C8">
-        <v>5.395966355911134</v>
+        <v>8.574292085683815</v>
       </c>
       <c r="D8">
-        <v>7.167034305475766</v>
+        <v>11.20775264568588</v>
       </c>
       <c r="E8">
-        <v>8.208600965738023</v>
+        <v>14.26388612992345</v>
       </c>
       <c r="F8">
-        <v>4.699571513283521</v>
+        <v>12.3694762556837</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -812,19 +812,19 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>7.051561759478334</v>
+        <v>12.75494521282979</v>
       </c>
       <c r="C9">
-        <v>2.98626963137933</v>
+        <v>3.072273636102473</v>
       </c>
       <c r="D9">
-        <v>1.799306421434648</v>
+        <v>2.639307402908763</v>
       </c>
       <c r="E9">
-        <v>2.248704934620537</v>
+        <v>3.726072827684587</v>
       </c>
       <c r="F9">
-        <v>1.252414575359276</v>
+        <v>4.008751788617897</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -832,19 +832,19 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>10.56042634163447</v>
+        <v>6.220445487696954</v>
       </c>
       <c r="C10">
-        <v>10.73160776291184</v>
+        <v>28.11655028352125</v>
       </c>
       <c r="D10">
-        <v>4.105508637371505</v>
+        <v>2.477758941866569</v>
       </c>
       <c r="E10">
-        <v>9.213185017297864</v>
+        <v>4.275960244132901</v>
       </c>
       <c r="F10">
-        <v>12.79705155210254</v>
+        <v>9.333552441399428</v>
       </c>
     </row>
   </sheetData>
@@ -882,19 +882,19 @@
         <v>16</v>
       </c>
       <c r="B2">
-        <v>312.7364552979616</v>
+        <v>602.7391674218293</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>47.97620685590375</v>
       </c>
       <c r="D2">
-        <v>32.70900205828086</v>
+        <v>81.46561644401419</v>
       </c>
       <c r="E2">
-        <v>3578.555880387605</v>
+        <v>4802.390514347499</v>
       </c>
       <c r="F2">
-        <v>160.7074429422057</v>
+        <v>315.5605256996824</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -902,19 +902,19 @@
         <v>17</v>
       </c>
       <c r="B3">
-        <v>1315.502551133894</v>
+        <v>421.5668875300298</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>9.43133941892528</v>
       </c>
       <c r="D3">
-        <v>2.339106679001917</v>
+        <v>3.587221479111307</v>
       </c>
       <c r="E3">
-        <v>1.507900905345171E-05</v>
+        <v>2.138503817672763</v>
       </c>
       <c r="F3">
-        <v>38.22459422835947</v>
+        <v>14.14640465244765</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -922,19 +922,19 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>438.0709466916866</v>
+        <v>675.0668273843058</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>18.6716211314194</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.06678312884669375</v>
       </c>
       <c r="E4">
-        <v>13.20957408283649</v>
+        <v>1.800010232447979</v>
       </c>
       <c r="F4">
-        <v>10.79791864911858</v>
+        <v>13.20302901669124</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -942,19 +942,19 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>1.163612339471819</v>
+        <v>114.151131271114</v>
       </c>
       <c r="C5">
-        <v>5567.694119299737</v>
+        <v>3610.505696744707</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>0.03369381697803368</v>
       </c>
       <c r="E5">
-        <v>0.04861143550294392</v>
+        <v>0.5210529685063257</v>
       </c>
       <c r="F5">
-        <v>888.8951793916627</v>
+        <v>245.6147503574026</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -982,19 +982,19 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>336.7124480665429</v>
+        <v>444.5542477768217</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>325.4115823689556</v>
       </c>
       <c r="D7">
-        <v>3.533601760788727</v>
+        <v>7.321989924503413</v>
       </c>
       <c r="E7">
-        <v>8.791957842930925</v>
+        <v>0.7451089934282693</v>
       </c>
       <c r="F7">
-        <v>95.20090487225919</v>
+        <v>114.4360677952683</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1002,19 +1002,19 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>477.1030916427846</v>
+        <v>728.0240623386992</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>22.31024241730355</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.03466229876483385</v>
       </c>
       <c r="E8">
-        <v>56.99019242517961</v>
+        <v>4.548072390358379</v>
       </c>
       <c r="F8">
-        <v>1.835198498241583</v>
+        <v>2.396578574003467</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1022,19 +1022,19 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>1851.568030356954</v>
+        <v>1490.9041037054</v>
       </c>
       <c r="C9">
-        <v>27.5319</v>
+        <v>226.9743336029269</v>
       </c>
       <c r="D9">
-        <v>4.437924827439155</v>
+        <v>3.008485983345205</v>
       </c>
       <c r="E9">
-        <v>175.6142497035181</v>
+        <v>43.44006506727275</v>
       </c>
       <c r="F9">
-        <v>241.0400083120736</v>
+        <v>84.79462044095942</v>
       </c>
     </row>
   </sheetData>
@@ -1072,19 +1072,19 @@
         <v>16</v>
       </c>
       <c r="B2">
-        <v>6.429467495239734</v>
+        <v>13.07953738132041</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1.125863481008001</v>
       </c>
       <c r="D2">
-        <v>76.03272740641856</v>
+        <v>85.28783059286729</v>
       </c>
       <c r="E2">
-        <v>93.35662359700562</v>
+        <v>98.90450209833801</v>
       </c>
       <c r="F2">
-        <v>10.86258691591351</v>
+        <v>37.88655389599599</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1092,19 +1092,19 @@
         <v>17</v>
       </c>
       <c r="B3">
-        <v>27.04507501168013</v>
+        <v>9.148069616516224</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>0.2213263891547636</v>
       </c>
       <c r="D3">
-        <v>5.437300110293651</v>
+        <v>3.755527192503309</v>
       </c>
       <c r="E3">
-        <v>3.933780607238852E-07</v>
+        <v>0.04404216081354167</v>
       </c>
       <c r="F3">
-        <v>2.583688530719782</v>
+        <v>1.6984333547777</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1112,19 +1112,19 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>9.006186725751558</v>
+        <v>14.64905929612999</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>0.4381692038768493</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.06991646817590555</v>
       </c>
       <c r="E4">
-        <v>0.3446086289407209</v>
+        <v>0.03707093691783412</v>
       </c>
       <c r="F4">
-        <v>0.7298562387007522</v>
+        <v>1.585170608149278</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1132,19 +1132,19 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>0.02392240363076944</v>
+        <v>2.477098004045316</v>
       </c>
       <c r="C5">
-        <v>99.50793944864724</v>
+        <v>84.72817628424075</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>0.03527466776642503</v>
       </c>
       <c r="E5">
-        <v>0.001268165047143795</v>
+        <v>0.01073100662326732</v>
       </c>
       <c r="F5">
-        <v>60.08247638381561</v>
+        <v>29.48878493732557</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1152,7 +1152,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>2.698420356824388</v>
+        <v>2.848236701735</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>2.89004739998922</v>
+        <v>5.133459330188054</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1172,19 +1172,19 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>6.92238369851647</v>
+        <v>9.646899050368784</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>7.6364731790202</v>
       </c>
       <c r="D7">
-        <v>8.213927742649414</v>
+        <v>7.66552397860868</v>
       </c>
       <c r="E7">
-        <v>0.229362772709963</v>
+        <v>0.01534540637289879</v>
       </c>
       <c r="F7">
-        <v>6.434848845304738</v>
+        <v>13.73932382879043</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1192,19 +1192,19 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>9.808638448220146</v>
+        <v>15.79823985653747</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.5235571721107579</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.03628858890481912</v>
       </c>
       <c r="E8">
-        <v>1.486748319934617</v>
+        <v>0.0936668590219201</v>
       </c>
       <c r="F8">
-        <v>0.124045301388264</v>
+        <v>0.2877359362634087</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1212,19 +1212,19 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>38.06590586013682</v>
+        <v>32.3528600933468</v>
       </c>
       <c r="C9">
-        <v>0.4920605513527712</v>
+        <v>5.3264342905887</v>
       </c>
       <c r="D9">
-        <v>10.31604474063839</v>
+        <v>3.149638511173566</v>
       </c>
       <c r="E9">
-        <v>4.58138812298388</v>
+        <v>0.8946415319125234</v>
       </c>
       <c r="F9">
-        <v>16.29245038416812</v>
+        <v>10.18053810850957</v>
       </c>
     </row>
   </sheetData>
@@ -1282,19 +1282,19 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>412.9581321090125</v>
+        <v>315.1104817762255</v>
       </c>
       <c r="C3">
-        <v>389.1303615014439</v>
+        <v>321.2145903686751</v>
       </c>
       <c r="D3">
-        <v>5.801537437292059</v>
+        <v>27.2799747685265</v>
       </c>
       <c r="E3">
-        <v>121.941115910655</v>
+        <v>281.0931174981073</v>
       </c>
       <c r="F3">
-        <v>10.64188207745017</v>
+        <v>29.28483623602856</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1302,19 +1302,19 @@
         <v>23</v>
       </c>
       <c r="B4">
-        <v>642.0608088897418</v>
+        <v>1524.700427995741</v>
       </c>
       <c r="C4">
-        <v>515.1106499279065</v>
+        <v>952.3211206275836</v>
       </c>
       <c r="D4">
-        <v>4.255098843274198</v>
+        <v>13.06343724149144</v>
       </c>
       <c r="E4">
-        <v>997.6042392695101</v>
+        <v>1632.008618721823</v>
       </c>
       <c r="F4">
-        <v>138.2326254470156</v>
+        <v>239.2734234314147</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1322,19 +1322,19 @@
         <v>24</v>
       </c>
       <c r="B5">
-        <v>1926.864799229101</v>
+        <v>823.3396835800909</v>
       </c>
       <c r="C5">
-        <v>2619.624402800421</v>
+        <v>759.7505715122435</v>
       </c>
       <c r="D5">
-        <v>23.2795048972046</v>
+        <v>39.30388070198669</v>
       </c>
       <c r="E5">
-        <v>878.8013370965516</v>
+        <v>1085.772877588233</v>
       </c>
       <c r="F5">
-        <v>407.2896920167967</v>
+        <v>163.6032514151345</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1342,19 +1342,19 @@
         <v>25</v>
       </c>
       <c r="B6">
-        <v>280.9846273953015</v>
+        <v>289.7720072197365</v>
       </c>
       <c r="C6">
-        <v>1594.52000801272</v>
+        <v>158.8772576340237</v>
       </c>
       <c r="D6">
-        <v>6.318406688230417</v>
+        <v>6.915729089940432</v>
       </c>
       <c r="E6">
-        <v>1079.854650892856</v>
+        <v>535.7716626120562</v>
       </c>
       <c r="F6">
-        <v>635.9242052066603</v>
+        <v>110.6581096290513</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1362,19 +1362,19 @@
         <v>26</v>
       </c>
       <c r="B7">
-        <v>92.12503282863821</v>
+        <v>184.7498530950906</v>
       </c>
       <c r="C7">
-        <v>87.65798803431832</v>
+        <v>94.88970634477877</v>
       </c>
       <c r="D7">
-        <v>2.342417493501372</v>
+        <v>4.327783146915223</v>
       </c>
       <c r="E7">
-        <v>575.1196890910694</v>
+        <v>943.1461003697204</v>
       </c>
       <c r="F7">
-        <v>51.24039023150898</v>
+        <v>56.05850182471625</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1382,19 +1382,19 @@
         <v>27</v>
       </c>
       <c r="B8">
-        <v>1262.480104714714</v>
+        <v>1223.950343398524</v>
       </c>
       <c r="C8">
-        <v>361.6507090229273</v>
+        <v>1946.695876052838</v>
       </c>
       <c r="D8">
-        <v>0.8315699660080151</v>
+        <v>4.436548126703395</v>
       </c>
       <c r="E8">
-        <v>178.0970486959332</v>
+        <v>375.9985510272476</v>
       </c>
       <c r="F8">
-        <v>236.1294978400436</v>
+        <v>234.030899925664</v>
       </c>
     </row>
   </sheetData>
@@ -1432,16 +1432,16 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>5.070562421917216</v>
+        <v>5.352080135334831</v>
       </c>
       <c r="C2">
-        <v>0.4920605513527712</v>
+        <v>0.6460944456460249</v>
       </c>
       <c r="D2">
-        <v>0.4442157599757188</v>
+        <v>0.200066054094095</v>
       </c>
       <c r="E2">
-        <v>0.04675975944719601</v>
+        <v>0.03691420533824446</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1452,19 +1452,19 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>8.489898898291679</v>
+        <v>6.837948400246535</v>
       </c>
       <c r="C3">
-        <v>6.954685300633217</v>
+        <v>7.537981857324199</v>
       </c>
       <c r="D3">
-        <v>13.48578943869323</v>
+        <v>28.55990009275546</v>
       </c>
       <c r="E3">
-        <v>3.181174540674444</v>
+        <v>5.789069994695608</v>
       </c>
       <c r="F3">
-        <v>0.7193093667527064</v>
+        <v>3.515970585774788</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1472,19 +1472,19 @@
         <v>23</v>
       </c>
       <c r="B4">
-        <v>13.19996127982854</v>
+        <v>33.08624579449104</v>
       </c>
       <c r="C4">
-        <v>9.206252761749461</v>
+        <v>22.34823555616865</v>
       </c>
       <c r="D4">
-        <v>9.891062095430925</v>
+        <v>13.67634925071189</v>
       </c>
       <c r="E4">
-        <v>26.0252924859101</v>
+        <v>33.61096923972444</v>
       </c>
       <c r="F4">
-        <v>9.343462138670972</v>
+        <v>28.72743804889308</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1492,19 +1492,19 @@
         <v>24</v>
       </c>
       <c r="B5">
-        <v>39.61391255957577</v>
+        <v>17.86660424769386</v>
       </c>
       <c r="C5">
-        <v>46.818920160946</v>
+        <v>17.82915906023389</v>
       </c>
       <c r="D5">
-        <v>54.1136732588708</v>
+        <v>41.14794517337272</v>
       </c>
       <c r="E5">
-        <v>22.92598701434332</v>
+        <v>22.36132724502824</v>
       </c>
       <c r="F5">
-        <v>27.5296501424589</v>
+        <v>19.64239154614233</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1512,19 +1512,19 @@
         <v>25</v>
       </c>
       <c r="B6">
-        <v>5.776689918605446</v>
+        <v>6.288099405755536</v>
       </c>
       <c r="C6">
-        <v>28.49786590412446</v>
+        <v>3.728391927066974</v>
       </c>
       <c r="D6">
-        <v>14.68726231736232</v>
+        <v>7.240202146562684</v>
       </c>
       <c r="E6">
-        <v>28.17102416518956</v>
+        <v>11.03413588935175</v>
       </c>
       <c r="F6">
-        <v>42.98358448447701</v>
+        <v>13.2857378951131</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1532,19 +1532,19 @@
         <v>26</v>
       </c>
       <c r="B7">
-        <v>1.893974603968989</v>
+        <v>4.009101681722195</v>
       </c>
       <c r="C7">
-        <v>1.566656784407952</v>
+        <v>2.226788278990695</v>
       </c>
       <c r="D7">
-        <v>5.4449961646056</v>
+        <v>4.530834626783117</v>
       </c>
       <c r="E7">
-        <v>15.0036031662824</v>
+        <v>19.42395046474692</v>
       </c>
       <c r="F7">
-        <v>3.463456217738838</v>
+        <v>6.730447181255405</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1552,19 +1552,19 @@
         <v>27</v>
       </c>
       <c r="B8">
-        <v>25.95500031781235</v>
+        <v>26.559920334756</v>
       </c>
       <c r="C8">
-        <v>6.463558536786135</v>
+        <v>45.68334887456955</v>
       </c>
       <c r="D8">
-        <v>1.933000965061398</v>
+        <v>4.644702655720028</v>
       </c>
       <c r="E8">
-        <v>4.646158868152973</v>
+        <v>7.74363296111482</v>
       </c>
       <c r="F8">
-        <v>15.96053764990159</v>
+        <v>28.09801474282128</v>
       </c>
     </row>
   </sheetData>

--- a/data/gold/results/01_eriksen_replication/full_results_tables.xlsx
+++ b/data/gold/results/01_eriksen_replication/full_results_tables.xlsx
@@ -474,7 +474,7 @@
         <v>1581.30551358638</v>
       </c>
       <c r="F2">
-        <v>168.4117598594563</v>
+        <v>33.90650118484526</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -494,7 +494,7 @@
         <v>14.75781639340486</v>
       </c>
       <c r="F3">
-        <v>2.366540851442613</v>
+        <v>0.7332514977434348</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -502,7 +502,7 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>606.2380000000001</v>
+        <v>627.294307534464</v>
       </c>
       <c r="C4">
         <v>27.5319</v>
@@ -534,7 +534,7 @@
         <v>130.9241583599658</v>
       </c>
       <c r="F5">
-        <v>50.96721475057531</v>
+        <v>7.926740843518588</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -542,7 +542,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>131.2541696372094</v>
+        <v>131.0762816237094</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -574,7 +574,7 @@
         <v>2045.663178932456</v>
       </c>
       <c r="F7">
-        <v>354.2507215739509</v>
+        <v>99.89802720108061</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -594,7 +594,7 @@
         <v>692.5948768233908</v>
       </c>
       <c r="F8">
-        <v>103.0264837648855</v>
+        <v>29.67655971303259</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -614,7 +614,7 @@
         <v>180.9225710033792</v>
       </c>
       <c r="F9">
-        <v>33.38925533550565</v>
+        <v>8.543723707461474</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -634,7 +634,7 @@
         <v>207.6228127182082</v>
       </c>
       <c r="F10">
-        <v>77.74000040063899</v>
+        <v>35.97624159870432</v>
       </c>
     </row>
   </sheetData>
@@ -672,7 +672,7 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>9.282264530973327</v>
+        <v>9.240399507631443</v>
       </c>
       <c r="C2">
         <v>3.286427011471938</v>
@@ -684,7 +684,7 @@
         <v>32.56674650246919</v>
       </c>
       <c r="F2">
-        <v>20.21970651268073</v>
+        <v>13.07021455840611</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -692,7 +692,7 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>1.589498673951277</v>
+        <v>1.582329690685952</v>
       </c>
       <c r="C3">
         <v>0.712296286253683</v>
@@ -704,7 +704,7 @@
         <v>0.3039349836477669</v>
       </c>
       <c r="F3">
-        <v>0.2841295732932891</v>
+        <v>0.2826524137224412</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -712,7 +712,7 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>13.15546261394286</v>
+        <v>13.5509930742379</v>
       </c>
       <c r="C4">
         <v>0.6460944456460246</v>
@@ -732,7 +732,7 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>4.294014899666319</v>
+        <v>4.274647962492198</v>
       </c>
       <c r="C5">
         <v>4.141744994803999</v>
@@ -744,7 +744,7 @@
         <v>2.696363125104114</v>
       </c>
       <c r="F5">
-        <v>6.119181492346005</v>
+        <v>3.055585210896829</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -752,7 +752,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>2.848236701734999</v>
+        <v>2.831547749031911</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>5.133459330188053</v>
+        <v>16.48190596499515</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -772,7 +772,7 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>36.59590090586916</v>
+        <v>36.43084546702348</v>
       </c>
       <c r="C7">
         <v>51.45032125651682</v>
@@ -784,7 +784,7 @@
         <v>42.13012198169974</v>
       </c>
       <c r="F7">
-        <v>42.53174260579089</v>
+        <v>38.50850438272881</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -792,7 +792,7 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>13.2592309733353</v>
+        <v>13.19942897002653</v>
       </c>
       <c r="C8">
         <v>8.574292085683815</v>
@@ -804,7 +804,7 @@
         <v>14.26388612992345</v>
       </c>
       <c r="F8">
-        <v>12.3694762556837</v>
+        <v>11.43966464396073</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -812,7 +812,7 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>12.75494521282979</v>
+        <v>12.69741764751663</v>
       </c>
       <c r="C9">
         <v>3.072273636102473</v>
@@ -824,7 +824,7 @@
         <v>3.726072827684587</v>
       </c>
       <c r="F9">
-        <v>4.008751788617897</v>
+        <v>3.293418609472254</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -832,7 +832,7 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>6.220445487696954</v>
+        <v>6.192389931353953</v>
       </c>
       <c r="C10">
         <v>28.11655028352125</v>
@@ -844,7 +844,7 @@
         <v>4.275960244132901</v>
       </c>
       <c r="F10">
-        <v>9.333552441399428</v>
+        <v>13.86805421581769</v>
       </c>
     </row>
   </sheetData>
@@ -894,7 +894,7 @@
         <v>4802.390514347499</v>
       </c>
       <c r="F2">
-        <v>315.5605256996824</v>
+        <v>48.16471787893404</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -914,7 +914,7 @@
         <v>2.138503817672763</v>
       </c>
       <c r="F3">
-        <v>14.14640465244765</v>
+        <v>14.13154481086062</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -934,7 +934,7 @@
         <v>1.800010232447979</v>
       </c>
       <c r="F4">
-        <v>13.20302901669124</v>
+        <v>13.19745430810626</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -954,7 +954,7 @@
         <v>0.5210529685063257</v>
       </c>
       <c r="F5">
-        <v>245.6147503574026</v>
+        <v>0.3138128612551062</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -962,7 +962,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>131.2541696372094</v>
+        <v>131.0762816237094</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -994,7 +994,7 @@
         <v>0.7451089934282693</v>
       </c>
       <c r="F7">
-        <v>114.4360677952683</v>
+        <v>67.99320431355137</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1014,7 +1014,7 @@
         <v>4.548072390358379</v>
       </c>
       <c r="F8">
-        <v>2.396578574003467</v>
+        <v>2.396510186014004</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1022,7 +1022,7 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>1490.9041037054</v>
+        <v>1511.960411239864</v>
       </c>
       <c r="C9">
         <v>226.9743336029269</v>
@@ -1034,7 +1034,7 @@
         <v>43.44006506727275</v>
       </c>
       <c r="F9">
-        <v>84.79462044095942</v>
+        <v>70.46380138766511</v>
       </c>
     </row>
   </sheetData>
@@ -1072,7 +1072,7 @@
         <v>16</v>
       </c>
       <c r="B2">
-        <v>13.07953738132041</v>
+        <v>13.02054583502878</v>
       </c>
       <c r="C2">
         <v>1.125863481008001</v>
@@ -1084,7 +1084,7 @@
         <v>98.90450209833801</v>
       </c>
       <c r="F2">
-        <v>37.88655389599599</v>
+        <v>18.56644521918811</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1092,7 +1092,7 @@
         <v>17</v>
       </c>
       <c r="B3">
-        <v>9.148069616516224</v>
+        <v>9.106809841301812</v>
       </c>
       <c r="C3">
         <v>0.2213263891547636</v>
@@ -1104,7 +1104,7 @@
         <v>0.04404216081354167</v>
       </c>
       <c r="F3">
-        <v>1.6984333547777</v>
+        <v>5.447401420534439</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1112,7 +1112,7 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>14.64905929612999</v>
+        <v>14.58298886608324</v>
       </c>
       <c r="C4">
         <v>0.4381692038768493</v>
@@ -1124,7 +1124,7 @@
         <v>0.03707093691783412</v>
       </c>
       <c r="F4">
-        <v>1.585170608149278</v>
+        <v>5.087329963399671</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1132,7 +1132,7 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>2.477098004045316</v>
+        <v>2.465925755569369</v>
       </c>
       <c r="C5">
         <v>84.72817628424075</v>
@@ -1144,7 +1144,7 @@
         <v>0.01073100662326732</v>
       </c>
       <c r="F5">
-        <v>29.48878493732557</v>
+        <v>0.1209679938791443</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1152,7 +1152,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>2.848236701735</v>
+        <v>2.831547749031911</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>5.133459330188054</v>
+        <v>16.48190596499514</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1172,7 +1172,7 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>9.646899050368784</v>
+        <v>9.603389446373672</v>
       </c>
       <c r="C7">
         <v>7.6364731790202</v>
@@ -1184,7 +1184,7 @@
         <v>0.01534540637289879</v>
       </c>
       <c r="F7">
-        <v>13.73932382879043</v>
+        <v>26.20989302455258</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1192,7 +1192,7 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>15.79823985653747</v>
+        <v>15.7269863732794</v>
       </c>
       <c r="C8">
         <v>0.5235571721107579</v>
@@ -1204,7 +1204,7 @@
         <v>0.0936668590219201</v>
       </c>
       <c r="F8">
-        <v>0.2877359362634087</v>
+        <v>0.92380225703172</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1212,7 +1212,7 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>32.3528600933468</v>
+        <v>32.6618061333318</v>
       </c>
       <c r="C9">
         <v>5.3264342905887</v>
@@ -1224,7 +1224,7 @@
         <v>0.8946415319125234</v>
       </c>
       <c r="F9">
-        <v>10.18053810850957</v>
+        <v>27.16225415641922</v>
       </c>
     </row>
   </sheetData>
@@ -1262,7 +1262,7 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>246.6378</v>
+        <v>255.2290121415143</v>
       </c>
       <c r="C2">
         <v>27.5319</v>
@@ -1294,7 +1294,7 @@
         <v>281.0931174981073</v>
       </c>
       <c r="F3">
-        <v>29.28483623602856</v>
+        <v>2.825676300080865</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1314,7 +1314,7 @@
         <v>1632.008618721823</v>
       </c>
       <c r="F4">
-        <v>239.2734234314147</v>
+        <v>72.36043674012282</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1334,7 +1334,7 @@
         <v>1085.772877588233</v>
       </c>
       <c r="F5">
-        <v>163.6032514151345</v>
+        <v>28.80136558843698</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1354,7 +1354,7 @@
         <v>535.7716626120562</v>
       </c>
       <c r="F6">
-        <v>110.6581096290513</v>
+        <v>9.61024487032582</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1374,7 +1374,7 @@
         <v>943.1461003697204</v>
       </c>
       <c r="F7">
-        <v>56.05850182471625</v>
+        <v>14.43208719300315</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1382,7 +1382,7 @@
         <v>27</v>
       </c>
       <c r="B8">
-        <v>1223.950343398524</v>
+        <v>1236.237550777973</v>
       </c>
       <c r="C8">
         <v>1946.695876052838</v>
@@ -1394,7 +1394,7 @@
         <v>375.9985510272476</v>
       </c>
       <c r="F8">
-        <v>234.030899925664</v>
+        <v>131.3882809799709</v>
       </c>
     </row>
   </sheetData>
@@ -1432,7 +1432,7 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>5.352080135334831</v>
+        <v>5.513530944458991</v>
       </c>
       <c r="C2">
         <v>0.6460944456460249</v>
@@ -1452,7 +1452,7 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>6.837948400246535</v>
+        <v>6.807107772032192</v>
       </c>
       <c r="C3">
         <v>7.537981857324199</v>
@@ -1464,7 +1464,7 @@
         <v>5.789069994695608</v>
       </c>
       <c r="F3">
-        <v>3.515970585774788</v>
+        <v>1.089236406709139</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1472,7 +1472,7 @@
         <v>23</v>
       </c>
       <c r="B4">
-        <v>33.08624579449104</v>
+        <v>32.93701966030151</v>
       </c>
       <c r="C4">
         <v>22.34823555616865</v>
@@ -1484,7 +1484,7 @@
         <v>33.61096923972444</v>
       </c>
       <c r="F4">
-        <v>28.72743804889308</v>
+        <v>27.89336559904606</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1492,7 +1492,7 @@
         <v>24</v>
       </c>
       <c r="B5">
-        <v>17.86660424769386</v>
+        <v>17.7860219930755</v>
       </c>
       <c r="C5">
         <v>17.82915906023389</v>
@@ -1504,7 +1504,7 @@
         <v>22.36132724502824</v>
       </c>
       <c r="F5">
-        <v>19.64239154614233</v>
+        <v>11.10229645234578</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1512,7 +1512,7 @@
         <v>25</v>
       </c>
       <c r="B6">
-        <v>6.288099405755536</v>
+        <v>6.259738715589937</v>
       </c>
       <c r="C6">
         <v>3.728391927066974</v>
@@ -1524,7 +1524,7 @@
         <v>11.03413588935175</v>
       </c>
       <c r="F6">
-        <v>13.2857378951131</v>
+        <v>3.704539189378862</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1532,7 +1532,7 @@
         <v>26</v>
       </c>
       <c r="B7">
-        <v>4.009101681722195</v>
+        <v>3.991019764866106</v>
       </c>
       <c r="C7">
         <v>2.226788278990695</v>
@@ -1544,7 +1544,7 @@
         <v>19.42395046474692</v>
       </c>
       <c r="F7">
-        <v>6.730447181255405</v>
+        <v>5.563253934985354</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1552,7 +1552,7 @@
         <v>27</v>
       </c>
       <c r="B8">
-        <v>26.559920334756</v>
+        <v>26.70556114967577</v>
       </c>
       <c r="C8">
         <v>45.68334887456955</v>
@@ -1564,7 +1564,7 @@
         <v>7.74363296111482</v>
       </c>
       <c r="F8">
-        <v>28.09801474282128</v>
+        <v>50.64730841753481</v>
       </c>
     </row>
   </sheetData>

--- a/data/gold/results/01_eriksen_replication/full_results_tables.xlsx
+++ b/data/gold/results/01_eriksen_replication/full_results_tables.xlsx
@@ -462,7 +462,7 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>427.7509388962222</v>
+        <v>434.2318219284023</v>
       </c>
       <c r="C2">
         <v>140.043890559487</v>
@@ -482,7 +482,7 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>73.2482410825739</v>
+        <v>74.20055145733954</v>
       </c>
       <c r="C3">
         <v>30.35294647038642</v>
@@ -522,7 +522,7 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>197.8793966534408</v>
+        <v>200.5605077192405</v>
       </c>
       <c r="C5">
         <v>176.4913934655891</v>
@@ -562,7 +562,7 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>1686.434481586272</v>
+        <v>1738.976663948076</v>
       </c>
       <c r="C7">
         <v>2192.44277573989</v>
@@ -582,7 +582,7 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>611.0199164181031</v>
+        <v>618.9703903228116</v>
       </c>
       <c r="C8">
         <v>365.374681464406</v>
@@ -602,7 +602,7 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>587.7811144201161</v>
+        <v>595.9829789959068</v>
       </c>
       <c r="C9">
         <v>130.9182134157388</v>
@@ -622,7 +622,7 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>286.654338371472</v>
+        <v>293.6223608991782</v>
       </c>
       <c r="C10">
         <v>1198.125221424649</v>
@@ -672,7 +672,7 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>9.240399507631443</v>
+        <v>9.209746990490107</v>
       </c>
       <c r="C2">
         <v>3.286427011471938</v>
@@ -692,7 +692,7 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>1.582329690685952</v>
+        <v>1.573740732409094</v>
       </c>
       <c r="C3">
         <v>0.712296286253683</v>
@@ -712,7 +712,7 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>13.5509930742379</v>
+        <v>13.30446450310976</v>
       </c>
       <c r="C4">
         <v>0.6460944456460246</v>
@@ -732,7 +732,7 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>4.274647962492198</v>
+        <v>4.253745209587614</v>
       </c>
       <c r="C5">
         <v>4.141744994803999</v>
@@ -752,7 +752,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>2.831547749031911</v>
+        <v>2.780034371611842</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -772,7 +772,7 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>36.43084546702348</v>
+        <v>36.88245376905844</v>
       </c>
       <c r="C7">
         <v>51.45032125651682</v>
@@ -792,7 +792,7 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>13.19942897002653</v>
+        <v>13.12792016062316</v>
       </c>
       <c r="C8">
         <v>8.574292085683815</v>
@@ -812,7 +812,7 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>12.69741764751663</v>
+        <v>12.6403735746845</v>
       </c>
       <c r="C9">
         <v>3.072273636102473</v>
@@ -832,7 +832,7 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>6.192389931353953</v>
+        <v>6.227520688425462</v>
       </c>
       <c r="C10">
         <v>28.11655028352125</v>
@@ -882,7 +882,7 @@
         <v>16</v>
       </c>
       <c r="B2">
-        <v>602.7391674218293</v>
+        <v>608.6331305647049</v>
       </c>
       <c r="C2">
         <v>47.97620685590375</v>
@@ -902,7 +902,7 @@
         <v>17</v>
       </c>
       <c r="B3">
-        <v>421.5668875300298</v>
+        <v>422.3646611513331</v>
       </c>
       <c r="C3">
         <v>9.43133941892528</v>
@@ -922,7 +922,7 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>675.0668273843058</v>
+        <v>742.773267491394</v>
       </c>
       <c r="C4">
         <v>18.6716211314194</v>
@@ -942,7 +942,7 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>114.151131271114</v>
+        <v>114.0377107241366</v>
       </c>
       <c r="C5">
         <v>3610.505696744707</v>
@@ -982,7 +982,7 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>444.5542477768217</v>
+        <v>445.1076810373472</v>
       </c>
       <c r="C7">
         <v>325.4115823689556</v>
@@ -1002,7 +1002,7 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>728.0240623386992</v>
+        <v>728.3173203499359</v>
       </c>
       <c r="C8">
         <v>22.31024241730355</v>
@@ -1022,7 +1022,7 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>1511.960411239864</v>
+        <v>1522.605811486565</v>
       </c>
       <c r="C9">
         <v>226.9743336029269</v>
@@ -1072,7 +1072,7 @@
         <v>16</v>
       </c>
       <c r="B2">
-        <v>13.02054583502878</v>
+        <v>12.90867425984063</v>
       </c>
       <c r="C2">
         <v>1.125863481008001</v>
@@ -1092,7 +1092,7 @@
         <v>17</v>
       </c>
       <c r="B3">
-        <v>9.106809841301812</v>
+        <v>8.958052981131452</v>
       </c>
       <c r="C3">
         <v>0.2213263891547636</v>
@@ -1112,7 +1112,7 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>14.58298886608324</v>
+        <v>15.75369081546332</v>
       </c>
       <c r="C4">
         <v>0.4381692038768493</v>
@@ -1132,7 +1132,7 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>2.465925755569369</v>
+        <v>2.418658444882856</v>
       </c>
       <c r="C5">
         <v>84.72817628424075</v>
@@ -1152,7 +1152,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>2.831547749031911</v>
+        <v>2.780034371611845</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1172,7 +1172,7 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>9.603389446373672</v>
+        <v>9.440416199054278</v>
       </c>
       <c r="C7">
         <v>7.6364731790202</v>
@@ -1192,7 +1192,7 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>15.7269863732794</v>
+        <v>15.44709049517937</v>
       </c>
       <c r="C8">
         <v>0.5235571721107579</v>
@@ -1212,7 +1212,7 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>32.6618061333318</v>
+        <v>32.29338243283625</v>
       </c>
       <c r="C9">
         <v>5.3264342905887</v>
@@ -1282,7 +1282,7 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>315.1104817762255</v>
+        <v>322.6510358688241</v>
       </c>
       <c r="C3">
         <v>321.2145903686751</v>
@@ -1302,7 +1302,7 @@
         <v>23</v>
       </c>
       <c r="B4">
-        <v>1524.700427995741</v>
+        <v>1560.118401934924</v>
       </c>
       <c r="C4">
         <v>952.3211206275836</v>
@@ -1322,7 +1322,7 @@
         <v>24</v>
       </c>
       <c r="B5">
-        <v>823.3396835800909</v>
+        <v>838.8627644905578</v>
       </c>
       <c r="C5">
         <v>759.7505715122435</v>
@@ -1342,7 +1342,7 @@
         <v>25</v>
       </c>
       <c r="B6">
-        <v>289.7720072197365</v>
+        <v>302.3214177722913</v>
       </c>
       <c r="C6">
         <v>158.8772576340237</v>
@@ -1362,7 +1362,7 @@
         <v>26</v>
       </c>
       <c r="B7">
-        <v>184.7498530950906</v>
+        <v>194.2118842958945</v>
       </c>
       <c r="C7">
         <v>94.88970634477877</v>
@@ -1382,7 +1382,7 @@
         <v>27</v>
       </c>
       <c r="B8">
-        <v>1236.237550777973</v>
+        <v>1241.521347925117</v>
       </c>
       <c r="C8">
         <v>1946.695876052838</v>
@@ -1432,7 +1432,7 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>5.513530944458991</v>
+        <v>5.41322516626534</v>
       </c>
       <c r="C2">
         <v>0.6460944456460249</v>
@@ -1452,7 +1452,7 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>6.807107772032192</v>
+        <v>6.843198164001392</v>
       </c>
       <c r="C3">
         <v>7.537981857324199</v>
@@ -1472,7 +1472,7 @@
         <v>23</v>
       </c>
       <c r="B4">
-        <v>32.93701966030151</v>
+        <v>33.08899769993714</v>
       </c>
       <c r="C4">
         <v>22.34823555616865</v>
@@ -1492,7 +1492,7 @@
         <v>24</v>
       </c>
       <c r="B5">
-        <v>17.7860219930755</v>
+        <v>17.79168045858919</v>
       </c>
       <c r="C5">
         <v>17.82915906023389</v>
@@ -1512,7 +1512,7 @@
         <v>25</v>
       </c>
       <c r="B6">
-        <v>6.259738715589937</v>
+        <v>6.412021475358737</v>
       </c>
       <c r="C6">
         <v>3.728391927066974</v>
@@ -1532,7 +1532,7 @@
         <v>26</v>
       </c>
       <c r="B7">
-        <v>3.991019764866106</v>
+        <v>4.119095438395685</v>
       </c>
       <c r="C7">
         <v>2.226788278990695</v>
@@ -1552,7 +1552,7 @@
         <v>27</v>
       </c>
       <c r="B8">
-        <v>26.70556114967577</v>
+        <v>26.33178159745253</v>
       </c>
       <c r="C8">
         <v>45.68334887456955</v>

--- a/data/gold/results/01_eriksen_replication/full_results_tables.xlsx
+++ b/data/gold/results/01_eriksen_replication/full_results_tables.xlsx
@@ -462,7 +462,7 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>434.2318219284023</v>
+        <v>434.0642065248904</v>
       </c>
       <c r="C2">
         <v>140.043890559487</v>
@@ -482,7 +482,7 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>74.20055145733954</v>
+        <v>74.19180225056225</v>
       </c>
       <c r="C3">
         <v>30.35294647038642</v>
@@ -522,7 +522,7 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>200.5605077192405</v>
+        <v>200.5039586864416</v>
       </c>
       <c r="C5">
         <v>176.4913934655891</v>
@@ -562,7 +562,7 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>1738.976663948076</v>
+        <v>1738.272712170876</v>
       </c>
       <c r="C7">
         <v>2192.44277573989</v>
@@ -582,7 +582,7 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>618.9703903228116</v>
+        <v>618.7150161230603</v>
       </c>
       <c r="C8">
         <v>365.374681464406</v>
@@ -602,7 +602,7 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>595.9829789959068</v>
+        <v>595.8496914135698</v>
       </c>
       <c r="C9">
         <v>130.9182134157388</v>
@@ -622,7 +622,7 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>293.6223608991782</v>
+        <v>293.399629626269</v>
       </c>
       <c r="C10">
         <v>1198.125221424649</v>
@@ -672,7 +672,7 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>9.209746990490107</v>
+        <v>9.209216059799541</v>
       </c>
       <c r="C2">
         <v>3.286427011471938</v>
@@ -692,7 +692,7 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>1.573740732409094</v>
+        <v>1.574072053214022</v>
       </c>
       <c r="C3">
         <v>0.712296286253683</v>
@@ -712,7 +712,7 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>13.30446450310976</v>
+        <v>13.30883478602596</v>
       </c>
       <c r="C4">
         <v>0.6460944456460246</v>
@@ -732,7 +732,7 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>4.253745209587614</v>
+        <v>4.253942731586827</v>
       </c>
       <c r="C5">
         <v>4.141744994803999</v>
@@ -752,7 +752,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>2.780034371611842</v>
+        <v>2.780947564075761</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -772,7 +772,7 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>36.88245376905844</v>
+        <v>36.87963378827317</v>
       </c>
       <c r="C7">
         <v>51.45032125651682</v>
@@ -792,7 +792,7 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>13.12792016062316</v>
+        <v>13.12681436817087</v>
       </c>
       <c r="C8">
         <v>8.574292085683815</v>
@@ -812,7 +812,7 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>12.6403735746845</v>
+        <v>12.64169785231483</v>
       </c>
       <c r="C9">
         <v>3.072273636102473</v>
@@ -832,7 +832,7 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>6.227520688425462</v>
+        <v>6.224840796539012</v>
       </c>
       <c r="C10">
         <v>28.11655028352125</v>
@@ -882,7 +882,7 @@
         <v>16</v>
       </c>
       <c r="B2">
-        <v>608.6331305647049</v>
+        <v>608.4505807192885</v>
       </c>
       <c r="C2">
         <v>47.97620685590375</v>
@@ -902,7 +902,7 @@
         <v>17</v>
       </c>
       <c r="B3">
-        <v>422.3646611513331</v>
+        <v>422.2766649539725</v>
       </c>
       <c r="C3">
         <v>9.43133941892528</v>
@@ -922,7 +922,7 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>742.773267491394</v>
+        <v>742.5808112291425</v>
       </c>
       <c r="C4">
         <v>18.6716211314194</v>
@@ -942,7 +942,7 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>114.0377107241366</v>
+        <v>114.0231419249754</v>
       </c>
       <c r="C5">
         <v>3610.505696744707</v>
@@ -982,7 +982,7 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>445.1076810373472</v>
+        <v>444.7995209269739</v>
       </c>
       <c r="C7">
         <v>325.4115823689556</v>
@@ -1002,7 +1002,7 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>728.3173203499359</v>
+        <v>728.2074435255545</v>
       </c>
       <c r="C8">
         <v>22.31024241730355</v>
@@ -1022,7 +1022,7 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>1522.605811486565</v>
+        <v>1521.953161050231</v>
       </c>
       <c r="C9">
         <v>226.9743336029269</v>
@@ -1072,7 +1072,7 @@
         <v>16</v>
       </c>
       <c r="B2">
-        <v>12.90867425984063</v>
+        <v>12.90904150889279</v>
       </c>
       <c r="C2">
         <v>1.125863481008001</v>
@@ -1092,7 +1092,7 @@
         <v>17</v>
       </c>
       <c r="B3">
-        <v>8.958052981131452</v>
+        <v>8.959128594607382</v>
       </c>
       <c r="C3">
         <v>0.2213263891547636</v>
@@ -1112,7 +1112,7 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>15.75369081546332</v>
+        <v>15.7547824254388</v>
       </c>
       <c r="C4">
         <v>0.4381692038768493</v>
@@ -1132,7 +1132,7 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>2.418658444882856</v>
+        <v>2.419143836371753</v>
       </c>
       <c r="C5">
         <v>84.72817628424075</v>
@@ -1152,7 +1152,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>2.780034371611845</v>
+        <v>2.780947564075758</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1172,7 +1172,7 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>9.440416199054278</v>
+        <v>9.436979207077135</v>
       </c>
       <c r="C7">
         <v>7.6364731790202</v>
@@ -1192,7 +1192,7 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>15.44709049517937</v>
+        <v>15.44983341858791</v>
       </c>
       <c r="C8">
         <v>0.5235571721107579</v>
@@ -1212,7 +1212,7 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>32.29338243283625</v>
+        <v>32.29014344494846</v>
       </c>
       <c r="C9">
         <v>5.3264342905887</v>
@@ -1282,7 +1282,7 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>322.6510358688241</v>
+        <v>322.5931977633233</v>
       </c>
       <c r="C3">
         <v>321.2145903686751</v>
@@ -1302,7 +1302,7 @@
         <v>23</v>
       </c>
       <c r="B4">
-        <v>1560.118401934924</v>
+        <v>1559.53249844508</v>
       </c>
       <c r="C4">
         <v>952.3211206275836</v>
@@ -1322,7 +1322,7 @@
         <v>24</v>
       </c>
       <c r="B5">
-        <v>838.8627644905578</v>
+        <v>838.5844860549095</v>
       </c>
       <c r="C5">
         <v>759.7505715122435</v>
@@ -1342,7 +1342,7 @@
         <v>25</v>
       </c>
       <c r="B6">
-        <v>302.3214177722913</v>
+        <v>302.2388297149406</v>
       </c>
       <c r="C6">
         <v>158.8772576340237</v>
@@ -1362,7 +1362,7 @@
         <v>26</v>
       </c>
       <c r="B7">
-        <v>194.2118842958945</v>
+        <v>194.1649776523015</v>
       </c>
       <c r="C7">
         <v>94.88970634477877</v>
@@ -1382,7 +1382,7 @@
         <v>27</v>
       </c>
       <c r="B8">
-        <v>1241.521347925117</v>
+        <v>1241.02460418178</v>
       </c>
       <c r="C8">
         <v>1946.695876052838</v>
@@ -1432,7 +1432,7 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>5.41322516626534</v>
+        <v>5.415003315657222</v>
       </c>
       <c r="C2">
         <v>0.6460944456460249</v>
@@ -1452,7 +1452,7 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>6.843198164001392</v>
+        <v>6.844218926523552</v>
       </c>
       <c r="C3">
         <v>7.537981857324199</v>
@@ -1472,7 +1472,7 @@
         <v>23</v>
       </c>
       <c r="B4">
-        <v>33.08899769993714</v>
+        <v>33.0874361778</v>
       </c>
       <c r="C4">
         <v>22.34823555616865</v>
@@ -1492,7 +1492,7 @@
         <v>24</v>
       </c>
       <c r="B5">
-        <v>17.79168045858919</v>
+        <v>17.79162068741728</v>
       </c>
       <c r="C5">
         <v>17.82915906023389</v>
@@ -1512,7 +1512,7 @@
         <v>25</v>
       </c>
       <c r="B6">
-        <v>6.412021475358737</v>
+        <v>6.412375502669418</v>
       </c>
       <c r="C6">
         <v>3.728391927066974</v>
@@ -1532,7 +1532,7 @@
         <v>26</v>
       </c>
       <c r="B7">
-        <v>4.119095438395685</v>
+        <v>4.11945330567969</v>
       </c>
       <c r="C7">
         <v>2.226788278990695</v>
@@ -1552,7 +1552,7 @@
         <v>27</v>
       </c>
       <c r="B8">
-        <v>26.33178159745253</v>
+        <v>26.32989208425284</v>
       </c>
       <c r="C8">
         <v>45.68334887456955</v>

--- a/data/gold/results/01_eriksen_replication/full_results_tables.xlsx
+++ b/data/gold/results/01_eriksen_replication/full_results_tables.xlsx
@@ -505,13 +505,13 @@
         <v>627.294307534464</v>
       </c>
       <c r="C4">
-        <v>27.5319</v>
+        <v>25.6351</v>
       </c>
       <c r="D4">
-        <v>0.1911</v>
+        <v>0.1776</v>
       </c>
       <c r="E4">
-        <v>1.7924</v>
+        <v>1.6692</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -675,13 +675,13 @@
         <v>9.209216059799541</v>
       </c>
       <c r="C2">
-        <v>3.286427011471938</v>
+        <v>3.287890531649895</v>
       </c>
       <c r="D2">
-        <v>21.02064861852112</v>
+        <v>21.02361996971507</v>
       </c>
       <c r="E2">
-        <v>32.56674650246919</v>
+        <v>32.56757283469383</v>
       </c>
       <c r="F2">
         <v>13.07021455840611</v>
@@ -695,13 +695,13 @@
         <v>1.574072053214022</v>
       </c>
       <c r="C3">
-        <v>0.712296286253683</v>
+        <v>0.7126134878784193</v>
       </c>
       <c r="D3">
-        <v>0.3033210883446589</v>
+        <v>0.3033639639711137</v>
       </c>
       <c r="E3">
-        <v>0.3039349836477669</v>
+        <v>0.3039426955409757</v>
       </c>
       <c r="F3">
         <v>0.2826524137224412</v>
@@ -715,13 +715,13 @@
         <v>13.30883478602596</v>
       </c>
       <c r="C4">
-        <v>0.6460944456460246</v>
+        <v>0.6018499074195316</v>
       </c>
       <c r="D4">
-        <v>0.2000660540940949</v>
+        <v>0.1859589416891106</v>
       </c>
       <c r="E4">
-        <v>0.03691420533824447</v>
+        <v>0.0343777923422142</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -735,13 +735,13 @@
         <v>4.253942731586827</v>
       </c>
       <c r="C5">
-        <v>4.141744994803999</v>
+        <v>4.143589407398798</v>
       </c>
       <c r="D5">
-        <v>2.732291364770544</v>
+        <v>2.732677584879937</v>
       </c>
       <c r="E5">
-        <v>2.696363125104114</v>
+        <v>2.696431541264122</v>
       </c>
       <c r="F5">
         <v>3.055585210896829</v>
@@ -775,13 +775,13 @@
         <v>36.87963378827317</v>
       </c>
       <c r="C7">
-        <v>51.45032125651682</v>
+        <v>51.47323324666856</v>
       </c>
       <c r="D7">
-        <v>59.41885388380837</v>
+        <v>59.42725297203992</v>
       </c>
       <c r="E7">
-        <v>42.13012198169974</v>
+        <v>42.13119097019754</v>
       </c>
       <c r="F7">
         <v>38.50850438272881</v>
@@ -795,13 +795,13 @@
         <v>13.12681436817087</v>
       </c>
       <c r="C8">
-        <v>8.574292085683815</v>
+        <v>8.578110411615073</v>
       </c>
       <c r="D8">
-        <v>11.20775264568588</v>
+        <v>11.20933690551581</v>
       </c>
       <c r="E8">
-        <v>14.26388612992345</v>
+        <v>14.2642480545866</v>
       </c>
       <c r="F8">
         <v>11.43966464396073</v>
@@ -815,13 +815,13 @@
         <v>12.64169785231483</v>
       </c>
       <c r="C9">
-        <v>3.072273636102473</v>
+        <v>3.073641788945347</v>
       </c>
       <c r="D9">
-        <v>2.639307402908763</v>
+        <v>2.639680479370159</v>
       </c>
       <c r="E9">
-        <v>3.726072827684587</v>
+        <v>3.72616737118001</v>
       </c>
       <c r="F9">
         <v>3.293418609472254</v>
@@ -835,13 +835,13 @@
         <v>6.224840796539012</v>
       </c>
       <c r="C10">
-        <v>28.11655028352125</v>
+        <v>28.12907121842436</v>
       </c>
       <c r="D10">
-        <v>2.477758941866569</v>
+        <v>2.478109182818876</v>
       </c>
       <c r="E10">
-        <v>4.275960244132901</v>
+        <v>4.276068740194698</v>
       </c>
       <c r="F10">
         <v>13.86805421581769</v>
@@ -1025,13 +1025,13 @@
         <v>1521.953161050231</v>
       </c>
       <c r="C9">
-        <v>226.9743336029269</v>
+        <v>225.0775336029268</v>
       </c>
       <c r="D9">
-        <v>3.008485983345205</v>
+        <v>2.994985983345205</v>
       </c>
       <c r="E9">
-        <v>43.44006506727275</v>
+        <v>43.31686506727274</v>
       </c>
       <c r="F9">
         <v>70.46380138766511</v>
@@ -1075,13 +1075,13 @@
         <v>12.90904150889279</v>
       </c>
       <c r="C2">
-        <v>1.125863481008001</v>
+        <v>1.126364853445705</v>
       </c>
       <c r="D2">
-        <v>85.28783059286729</v>
+        <v>85.29988636249941</v>
       </c>
       <c r="E2">
-        <v>98.90450209833801</v>
+        <v>98.90701165136446</v>
       </c>
       <c r="F2">
         <v>18.56644521918811</v>
@@ -1095,13 +1095,13 @@
         <v>8.959128594607382</v>
       </c>
       <c r="C3">
-        <v>0.2213263891547636</v>
+        <v>0.2214249507949009</v>
       </c>
       <c r="D3">
-        <v>3.755527192503309</v>
+        <v>3.75605805101343</v>
       </c>
       <c r="E3">
-        <v>0.04404216081354167</v>
+        <v>0.04404327831714985</v>
       </c>
       <c r="F3">
         <v>5.447401420534439</v>
@@ -1115,13 +1115,13 @@
         <v>15.7547824254388</v>
       </c>
       <c r="C4">
-        <v>0.4381692038768493</v>
+        <v>0.4383643305201597</v>
       </c>
       <c r="D4">
-        <v>0.06991646817590555</v>
+        <v>0.06992635114312326</v>
       </c>
       <c r="E4">
-        <v>0.03707093691783412</v>
+        <v>0.03707187753711799</v>
       </c>
       <c r="F4">
         <v>5.087329963399671</v>
@@ -1135,13 +1135,13 @@
         <v>2.419143836371753</v>
       </c>
       <c r="C5">
-        <v>84.72817628424075</v>
+        <v>84.76590765487536</v>
       </c>
       <c r="D5">
-        <v>0.03527466776642503</v>
+        <v>0.03527965397917643</v>
       </c>
       <c r="E5">
-        <v>0.01073100662326732</v>
+        <v>0.01073127890642508</v>
       </c>
       <c r="F5">
         <v>0.1209679938791443</v>
@@ -1175,13 +1175,13 @@
         <v>9.436979207077135</v>
       </c>
       <c r="C7">
-        <v>7.6364731790202</v>
+        <v>7.639873873010028</v>
       </c>
       <c r="D7">
-        <v>7.66552397860868</v>
+        <v>7.666607530512311</v>
       </c>
       <c r="E7">
-        <v>0.01534540637289879</v>
+        <v>0.01534579573951191</v>
       </c>
       <c r="F7">
         <v>26.20989302455258</v>
@@ -1195,13 +1195,13 @@
         <v>15.44983341858791</v>
       </c>
       <c r="C8">
-        <v>0.5235571721107579</v>
+        <v>0.5237903239449607</v>
       </c>
       <c r="D8">
-        <v>0.03628858890481912</v>
+        <v>0.03629371843930334</v>
       </c>
       <c r="E8">
-        <v>0.0936668590219201</v>
+        <v>0.09366923567762887</v>
       </c>
       <c r="F8">
         <v>0.92380225703172</v>
@@ -1215,13 +1215,13 @@
         <v>32.29014344494846</v>
       </c>
       <c r="C9">
-        <v>5.3264342905887</v>
+        <v>5.284274013408887</v>
       </c>
       <c r="D9">
-        <v>3.149638511173566</v>
+        <v>3.13594833241326</v>
       </c>
       <c r="E9">
-        <v>0.8946415319125234</v>
+        <v>0.8921268824577132</v>
       </c>
       <c r="F9">
         <v>27.16225415641922</v>
@@ -1262,16 +1262,16 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>255.2290121415143</v>
+        <v>255.2290104137513</v>
       </c>
       <c r="C2">
-        <v>27.5319</v>
+        <v>25.6351</v>
       </c>
       <c r="D2">
-        <v>0.1911</v>
+        <v>0.1776</v>
       </c>
       <c r="E2">
-        <v>1.7924</v>
+        <v>1.6692</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1382,7 +1382,7 @@
         <v>27</v>
       </c>
       <c r="B8">
-        <v>1241.02460418178</v>
+        <v>1241.024605909543</v>
       </c>
       <c r="C8">
         <v>1946.695876052838</v>
@@ -1432,16 +1432,16 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>5.415003315657222</v>
+        <v>5.415003279000564</v>
       </c>
       <c r="C2">
-        <v>0.6460944456460249</v>
+        <v>0.6018499074195319</v>
       </c>
       <c r="D2">
-        <v>0.200066054094095</v>
+        <v>0.1859589416891107</v>
       </c>
       <c r="E2">
-        <v>0.03691420533824446</v>
+        <v>0.03437779234221418</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1455,13 +1455,13 @@
         <v>6.844218926523552</v>
       </c>
       <c r="C3">
-        <v>7.537981857324199</v>
+        <v>7.541338690903879</v>
       </c>
       <c r="D3">
-        <v>28.55990009275546</v>
+        <v>28.5639371467389</v>
       </c>
       <c r="E3">
-        <v>5.789069994695608</v>
+        <v>5.78921688364219</v>
       </c>
       <c r="F3">
         <v>1.089236406709139</v>
@@ -1475,13 +1475,13 @@
         <v>33.0874361778</v>
       </c>
       <c r="C4">
-        <v>22.34823555616865</v>
+        <v>22.35818773023612</v>
       </c>
       <c r="D4">
-        <v>13.67634925071189</v>
+        <v>13.67828245636184</v>
       </c>
       <c r="E4">
-        <v>33.61096923972444</v>
+        <v>33.61182206753093</v>
       </c>
       <c r="F4">
         <v>27.89336559904606</v>
@@ -1495,13 +1495,13 @@
         <v>17.79162068741728</v>
       </c>
       <c r="C5">
-        <v>17.82915906023389</v>
+        <v>17.83709878746641</v>
       </c>
       <c r="D5">
-        <v>41.14794517337272</v>
+        <v>41.15376159693979</v>
       </c>
       <c r="E5">
-        <v>22.36132724502824</v>
+        <v>22.36189463008425</v>
       </c>
       <c r="F5">
         <v>11.10229645234578</v>
@@ -1515,13 +1515,13 @@
         <v>6.412375502669418</v>
       </c>
       <c r="C6">
-        <v>3.728391927066974</v>
+        <v>3.730052264204403</v>
       </c>
       <c r="D6">
-        <v>7.240202146562684</v>
+        <v>7.241225577555852</v>
       </c>
       <c r="E6">
-        <v>11.03413588935175</v>
+        <v>11.03441586395884</v>
       </c>
       <c r="F6">
         <v>3.704539189378862</v>
@@ -1535,13 +1535,13 @@
         <v>4.11945330567969</v>
       </c>
       <c r="C7">
-        <v>2.226788278990695</v>
+        <v>2.22777991810727</v>
       </c>
       <c r="D7">
-        <v>4.530834626783117</v>
+        <v>4.531475078042365</v>
       </c>
       <c r="E7">
-        <v>19.42395046474692</v>
+        <v>19.42444331828381</v>
       </c>
       <c r="F7">
         <v>5.563253934985354</v>
@@ -1552,16 +1552,16 @@
         <v>27</v>
       </c>
       <c r="B8">
-        <v>26.32989208425284</v>
+        <v>26.3298921209095</v>
       </c>
       <c r="C8">
-        <v>45.68334887456955</v>
+        <v>45.70369270166238</v>
       </c>
       <c r="D8">
-        <v>4.644702655720028</v>
+        <v>4.645359202672129</v>
       </c>
       <c r="E8">
-        <v>7.74363296111482</v>
+        <v>7.743829444157765</v>
       </c>
       <c r="F8">
         <v>50.64730841753481</v>
